--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -718,7 +718,7 @@
     <t>HL7 Observation Interpretation Codes</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
   </si>
   <si>
     <t>FRLMObservation.note</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="206">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,116 +426,6 @@
   </si>
   <si>
     <t>FRLMEntry.header.status</t>
-  </si>
-  <si>
-    <t>FRLMObservation.header.status.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>FRLMObservation.header.status.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>FRLMObservation.header.status.coding</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>FRLMObservation.header.status.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>FRLMObservation.header.status.directSubject[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProcedure</t>
-  </si>
-  <si>
-    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
   </si>
   <si>
     <t>FRLMObservation.header.source</t>
@@ -558,6 +448,16 @@
     <t>FRLMEntry.header.language</t>
   </si>
   <si>
+    <t>FRLMObservation.header.directSubject[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProcedure</t>
+  </si>
+  <si>
+    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
+  </si>
+  <si>
     <t>FRLMObservation.observationDate[x]</t>
   </si>
   <si>
@@ -581,6 +481,10 @@
   </si>
   <si>
     <t>FRLMObservation.originalName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
   </si>
   <si>
     <t>Nom de l'observation</t>
@@ -1052,13 +956,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ46"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.0234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.0234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -1069,7 +973,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1083,7 +987,7 @@
     <col min="26" max="26" width="80.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="45.63671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2830,13 +2734,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>136</v>
-      </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2887,7 +2791,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2904,21 +2808,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
@@ -2930,17 +2834,15 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>72</v>
@@ -2977,39 +2879,39 @@
         <v>72</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>149</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3020,7 +2922,7 @@
         <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
@@ -3029,23 +2931,19 @@
         <v>72</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>72</v>
       </c>
@@ -3093,27 +2991,27 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3121,7 +3019,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>78</v>
@@ -3133,23 +3031,19 @@
         <v>72</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>72</v>
       </c>
@@ -3197,10 +3091,10 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>78</v>
@@ -3209,15 +3103,15 @@
         <v>72</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3225,7 +3119,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>78</v>
@@ -3240,13 +3134,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3273,10 +3167,10 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>72</v>
@@ -3297,10 +3191,10 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>78</v>
@@ -3314,10 +3208,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3340,13 +3234,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3397,7 +3291,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3414,10 +3308,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3443,10 +3337,10 @@
         <v>130</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3497,7 +3391,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3514,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3525,7 +3419,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>78</v>
@@ -3540,13 +3434,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3597,10 +3491,10 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>78</v>
@@ -3614,10 +3508,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3625,7 +3519,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>78</v>
@@ -3640,13 +3534,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3673,10 +3567,10 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>72</v>
@@ -3697,10 +3591,10 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
@@ -3714,10 +3608,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3740,13 +3634,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3797,7 +3691,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
@@ -3814,10 +3708,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3825,7 +3719,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
@@ -3840,13 +3734,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3897,10 +3791,10 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
@@ -3914,10 +3808,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3940,13 +3834,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3997,7 +3891,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -4014,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4028,7 +3922,7 @@
         <v>73</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>72</v>
@@ -4040,13 +3934,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4097,13 +3991,13 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>72</v>
@@ -4114,10 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4140,13 +4034,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4173,10 +4067,10 @@
         <v>72</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>72</v>
@@ -4197,7 +4091,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4214,10 +4108,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4225,7 +4119,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
@@ -4240,13 +4134,13 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4273,10 +4167,10 @@
         <v>72</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>72</v>
@@ -4297,10 +4191,10 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>78</v>
@@ -4314,10 +4208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4340,13 +4234,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4373,10 +4267,10 @@
         <v>72</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>72</v>
@@ -4397,7 +4291,7 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4414,10 +4308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4428,7 +4322,7 @@
         <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4440,13 +4334,13 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4473,10 +4367,10 @@
         <v>72</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>72</v>
@@ -4497,13 +4391,13 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>72</v>
@@ -4514,10 +4408,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4528,7 +4422,7 @@
         <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>72</v>
@@ -4540,13 +4434,13 @@
         <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4573,10 +4467,10 @@
         <v>72</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>72</v>
@@ -4597,13 +4491,13 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>72</v>
@@ -4614,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4640,13 +4534,13 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4673,10 +4567,10 @@
         <v>72</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>72</v>
@@ -4697,7 +4591,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -4714,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4740,13 +4634,13 @@
         <v>72</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4773,10 +4667,10 @@
         <v>72</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>210</v>
+        <v>72</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>72</v>
@@ -4797,7 +4691,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4814,10 +4708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4828,7 +4722,7 @@
         <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -4843,10 +4737,10 @@
         <v>130</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4873,13 +4767,13 @@
         <v>72</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>72</v>
@@ -4897,13 +4791,13 @@
         <v>72</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>72</v>
@@ -4914,10 +4808,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4928,7 +4822,7 @@
         <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
@@ -4940,13 +4834,13 @@
         <v>72</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4973,10 +4867,10 @@
         <v>72</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>72</v>
@@ -4997,13 +4891,13 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>72</v>
@@ -5014,10 +4908,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5028,7 +4922,7 @@
         <v>73</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>72</v>
@@ -5040,13 +4934,13 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5073,10 +4967,10 @@
         <v>72</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>72</v>
@@ -5097,13 +4991,13 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>72</v>
@@ -5114,10 +5008,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5128,7 +5022,7 @@
         <v>73</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>72</v>
@@ -5140,13 +5034,13 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5197,13 +5091,13 @@
         <v>72</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>72</v>
@@ -5214,10 +5108,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5240,13 +5134,13 @@
         <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5273,13 +5167,13 @@
         <v>72</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>224</v>
+        <v>72</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>225</v>
+        <v>72</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>72</v>
@@ -5297,7 +5191,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5309,406 +5203,6 @@
         <v>72</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,7 +532,7 @@
     <t>Valeur de l'observation</t>
   </si>
   <si>
-    <t>FRLMObservation.result.Value[x]</t>
+    <t>FRLMObservation.result.value[x]</t>
   </si>
   <si>
     <t>string
@@ -604,7 +604,7 @@
 </t>
   </si>
   <si>
-    <t>Tranche d'âge pour cet intervalle</t>
+    <t>Tranche d'âge pour cet intervalle. (preferred): UCUM for units</t>
   </si>
   <si>
     <t>FRLMObservation.referenceRange.text</t>
@@ -4567,10 +4567,10 @@
         <v>72</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>72</v>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
